--- a/data/trans_bre/P12_2_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,42</t>
+          <t>2,79; 10,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 6,73</t>
+          <t>-1,17; 6,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,51</t>
+          <t>-0,25; 7,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 17,99</t>
+          <t>5,21; 17,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,31; 165,16</t>
+          <t>25,86; 156,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 109,48</t>
+          <t>-13,9; 102,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 152,08</t>
+          <t>-4,48; 156,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,66; 998,12</t>
+          <t>48,38; 845,44</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 10,63</t>
+          <t>2,49; 10,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 9,05</t>
+          <t>1,77; 9,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,91</t>
+          <t>-1,34; 5,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 6,25</t>
+          <t>-3,83; 6,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,23; 102,76</t>
+          <t>17,34; 97,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,84; 118,01</t>
+          <t>15,85; 115,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 90,25</t>
+          <t>-13,67; 80,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,9; 91,28</t>
+          <t>-31,13; 100,42</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,38</t>
+          <t>0,17; 8,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,19</t>
+          <t>0,89; 9,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,27</t>
+          <t>0,98; 8,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 4,69</t>
+          <t>-3,36; 4,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 63,89</t>
+          <t>0,52; 59,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 74,38</t>
+          <t>4,84; 73,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 102,54</t>
+          <t>8,15; 102,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 41,31</t>
+          <t>-20,17; 40,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 16,43</t>
+          <t>5,62; 15,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 15,29</t>
+          <t>5,45; 15,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 8,53</t>
+          <t>-0,25; 8,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 16,62</t>
+          <t>2,31; 17,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,84; 107,78</t>
+          <t>26,02; 103,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,49; 109,88</t>
+          <t>28,9; 111,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 62,77</t>
+          <t>-1,57; 62,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 298,28</t>
+          <t>11,97; 270,32</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 13,2</t>
+          <t>0,55; 13,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 15,09</t>
+          <t>2,99; 14,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 15,44</t>
+          <t>3,56; 14,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,13</t>
+          <t>2,49; 11,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 50,88</t>
+          <t>1,35; 51,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,5; 72,05</t>
+          <t>10,62; 71,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 95,88</t>
+          <t>16,47; 91,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 59,07</t>
+          <t>10,38; 60,55</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,44; 26,98</t>
+          <t>12,58; 27,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 16,34</t>
+          <t>1,67; 17,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 16,01</t>
+          <t>2,53; 16,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 9,7</t>
+          <t>-16,07; 10,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,17; 92,65</t>
+          <t>34,26; 96,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 67,54</t>
+          <t>5,05; 71,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,58; 67,62</t>
+          <t>7,2; 69,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,84; 43,27</t>
+          <t>-63,0; 45,77</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 18,07</t>
+          <t>0,68; 18,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 15,0</t>
+          <t>-1,48; 14,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 12,95</t>
+          <t>-2,4; 13,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 11,31</t>
+          <t>0,03; 12,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 43,55</t>
+          <t>1,53; 44,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 40,06</t>
+          <t>-3,07; 40,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 33,83</t>
+          <t>-5,19; 37,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 34,84</t>
+          <t>0,05; 39,77</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,2</t>
+          <t>8,19; 12,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,22</t>
+          <t>6,34; 10,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,46</t>
+          <t>4,59; 8,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,17</t>
+          <t>1,97; 9,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,8; 65,85</t>
+          <t>39,95; 65,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,8; 62,21</t>
+          <t>34,54; 63,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,55; 57,18</t>
+          <t>27,75; 58,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,92; 70,41</t>
+          <t>13,01; 67,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_2_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P12_2_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,21</t>
+          <t>11,61</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>265,08%</t>
+          <t>268,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 10,79</t>
+          <t>3,27; 11,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 6,61</t>
+          <t>-1,56; 6,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 7,77</t>
+          <t>-0,18; 7,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 17,81</t>
+          <t>5,02; 17,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,86; 156,28</t>
+          <t>27,57; 170,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 102,02</t>
+          <t>-16,23; 104,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 156,43</t>
+          <t>-2,52; 154,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48,38; 845,44</t>
+          <t>56,72; 746,55</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>2,57</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 10,14</t>
+          <t>2,41; 10,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,05</t>
+          <t>2,02; 9,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 5,76</t>
+          <t>-1,46; 5,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 6,7</t>
+          <t>-2,7; 6,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,34; 97,4</t>
+          <t>16,24; 95,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 115,15</t>
+          <t>17,79; 117,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 80,69</t>
+          <t>-14,21; 84,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 100,42</t>
+          <t>-19,79; 88,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 8,84</t>
+          <t>0,11; 8,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,17</t>
+          <t>0,97; 9,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,08</t>
+          <t>1,06; 8,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,67</t>
+          <t>-1,34; 6,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 59,95</t>
+          <t>-0,05; 57,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 73,66</t>
+          <t>5,38; 77,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,15; 102,26</t>
+          <t>9,9; 101,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 40,85</t>
+          <t>-8,81; 57,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,3</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 15,98</t>
+          <t>5,16; 16,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 15,4</t>
+          <t>4,76; 15,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 8,25</t>
+          <t>-0,03; 8,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 17,33</t>
+          <t>0,38; 7,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,02; 103,4</t>
+          <t>26,32; 101,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,9; 111,59</t>
+          <t>25,78; 110,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 62,99</t>
+          <t>-1,39; 64,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,97; 270,32</t>
+          <t>2,15; 53,29</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>7,07</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 13,48</t>
+          <t>0,25; 13,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 14,76</t>
+          <t>2,36; 15,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,71</t>
+          <t>3,59; 15,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 11,07</t>
+          <t>2,58; 11,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 51,0</t>
+          <t>0,41; 54,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 71,91</t>
+          <t>9,39; 77,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,47; 91,27</t>
+          <t>16,9; 92,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 60,55</t>
+          <t>10,52; 60,81</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-9,77%</t>
+          <t>42,65%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,58; 27,41</t>
+          <t>12,93; 27,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 17,12</t>
+          <t>1,24; 15,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 16,22</t>
+          <t>1,6; 15,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 10,12</t>
+          <t>4,97; 14,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,26; 96,11</t>
+          <t>37,06; 97,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,05; 71,56</t>
+          <t>3,54; 66,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,2; 69,91</t>
+          <t>5,37; 67,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,0; 45,77</t>
+          <t>19,71; 70,66</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 18,34</t>
+          <t>1,72; 19,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 14,97</t>
+          <t>-1,23; 15,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 13,5</t>
+          <t>-2,45; 13,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 12,34</t>
+          <t>-0,19; 11,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 44,19</t>
+          <t>2,91; 44,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 40,02</t>
+          <t>-2,6; 42,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 37,48</t>
+          <t>-5,68; 35,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 39,77</t>
+          <t>-0,52; 33,6</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,75</t>
+          <t>6,62</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,3</t>
+          <t>8,19; 12,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,22</t>
+          <t>6,13; 10,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,48</t>
+          <t>4,64; 8,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,01</t>
+          <t>4,71; 8,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>39,95; 65,62</t>
+          <t>40,29; 65,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,54; 63,0</t>
+          <t>33,59; 61,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,75; 58,56</t>
+          <t>27,52; 57,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,01; 67,96</t>
+          <t>26,29; 52,0</t>
         </is>
       </c>
     </row>
